--- a/Databases/Database3BandReview/Winter Birds 2019 Band Review.xlsx
+++ b/Databases/Database3BandReview/Winter Birds 2019 Band Review.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rohanpoudel/Documents/USFWS/PipingPlover/Databases/Database3BandReview/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE18E869-643E-874C-B2AF-5C1CC9EA9D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862C58B3-9DA7-834B-9C89-8829684F5D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19820" yWindow="-28200" windowWidth="34400" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="250">
   <si>
     <t>What transect did you survey? (they are in alphabetical order by county, if your transect is not bellow, then choose "other"  at the end and enter the name of the transect in the comment box at the end of this section)</t>
   </si>
@@ -413,9 +413,6 @@
   </si>
   <si>
     <t>The banded PIPL and the other 6 PIPL seen foraging with it on this survey were probably among the loafing flock of PIPL reported 1.5 hours later on the Crandon Park survey, where a PIPL with the same color flag/band combination was seen.</t>
-  </si>
-  <si>
-    <t>UL: (code not readable) GF; LL: - ; UR:O: LR: -  (band not reported to another site)</t>
   </si>
   <si>
     <t>Caladesi Island State Park, County=Pinellas</t>
@@ -658,10 +655,6 @@
     <t>John Kendall</t>
   </si>
   <si>
-    <t>1) U9 white letters over black flag on upper left, metal band on lower right. turned into banded birds. org
-2) also I documented this individual here on 1/7/19</t>
-  </si>
-  <si>
     <t>1) white letters black flag U9  banded in N. Nova Scotia</t>
   </si>
   <si>
@@ -669,9 +662,6 @@
   </si>
   <si>
     <t>Jeff Liechty</t>
-  </si>
-  <si>
-    <t>7 banded PIPL all reported directly to banders</t>
   </si>
   <si>
     <t>1) GFE 97</t>
@@ -737,9 +727,6 @@
   </si>
   <si>
     <t>Ryan Welsh</t>
-  </si>
-  <si>
-    <t>Green Flag Upper Left, Blue band upper right, unable to read code on flag</t>
   </si>
   <si>
     <t>Three Rooker South Island, County=Pinellas</t>
@@ -793,6 +780,15 @@
 2) CC2, Horizontal, FG, Upper Left; O, Upper Right -
 3) S, Upper Left; 3H, Horizontal, FK, Upper Right -
 4) S, Upper Left; YG, Lower Left; GK, Lower Right -</t>
+  </si>
+  <si>
+    <t>1)UL: (code not readable) GF; LL: - ; UR:O: LR: -  (band not reported to another site)</t>
+  </si>
+  <si>
+    <t>1)Green Flag Upper Left, Blue band upper right, unable to read code on flag</t>
+  </si>
+  <si>
+    <t>1) U9 white letters over black flag on upper left, metal band on lower right. turned into banded birds. Org ,also I documented this individual here on 1/7/19</t>
   </si>
 </sst>
 </file>
@@ -1147,6 +1143,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="16" max="16" width="14.1640625" customWidth="1"/>
+    <col min="20" max="20" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:89" x14ac:dyDescent="0.2">
@@ -1949,21 +1946,21 @@
         <v>7</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>131</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:89" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B11" s="1">
         <v>43497</v>
       </c>
       <c r="C11" t="s">
+        <v>132</v>
+      </c>
+      <c r="H11" t="s">
         <v>133</v>
-      </c>
-      <c r="H11" t="s">
-        <v>134</v>
       </c>
       <c r="I11" t="s">
         <v>102</v>
@@ -1978,7 +1975,7 @@
         <v>95</v>
       </c>
       <c r="M11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N11">
         <v>25</v>
@@ -2011,7 +2008,7 @@
         <v>17</v>
       </c>
       <c r="Y11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Z11">
         <v>28.042507000000001</v>
@@ -2088,19 +2085,19 @@
     </row>
     <row r="12" spans="1:89" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B12" s="1">
         <v>43502</v>
       </c>
       <c r="C12" t="s">
+        <v>137</v>
+      </c>
+      <c r="H12" t="s">
         <v>138</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>139</v>
-      </c>
-      <c r="J12" t="s">
-        <v>140</v>
       </c>
       <c r="K12" t="s">
         <v>104</v>
@@ -2118,18 +2115,18 @@
         <v>5</v>
       </c>
       <c r="Q12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:89" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B13" s="1">
         <v>43500</v>
       </c>
       <c r="C13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D13">
         <v>29.211497000000001</v>
@@ -2144,7 +2141,7 @@
         <v>-83.055842999999996</v>
       </c>
       <c r="H13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I13" t="s">
         <v>102</v>
@@ -2159,7 +2156,7 @@
         <v>95</v>
       </c>
       <c r="M13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N13">
         <v>3</v>
@@ -2218,13 +2215,13 @@
     </row>
     <row r="14" spans="1:89" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B14" s="1">
         <v>43501</v>
       </c>
       <c r="C14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D14">
         <v>26.092046</v>
@@ -2242,10 +2239,10 @@
         <v>114</v>
       </c>
       <c r="I14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K14" t="s">
         <v>104</v>
@@ -2254,7 +2251,7 @@
         <v>95</v>
       </c>
       <c r="M14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N14">
         <v>2</v>
@@ -2268,13 +2265,13 @@
     </row>
     <row r="15" spans="1:89" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B15" s="1">
         <v>43497</v>
       </c>
       <c r="C15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D15">
         <v>29.079022999999999</v>
@@ -2289,13 +2286,13 @@
         <v>-80.094851000000006</v>
       </c>
       <c r="H15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I15" t="s">
         <v>102</v>
       </c>
       <c r="J15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K15" t="s">
         <v>104</v>
@@ -2304,7 +2301,7 @@
         <v>95</v>
       </c>
       <c r="M15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N15">
         <v>4</v>
@@ -2381,19 +2378,19 @@
     </row>
     <row r="16" spans="1:89" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B16" s="1">
         <v>43501</v>
       </c>
       <c r="C16" t="s">
+        <v>154</v>
+      </c>
+      <c r="H16" t="s">
         <v>155</v>
       </c>
-      <c r="H16" t="s">
-        <v>156</v>
-      </c>
       <c r="J16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K16" t="s">
         <v>104</v>
@@ -2440,22 +2437,22 @@
     </row>
     <row r="17" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B17" s="1">
         <v>43501</v>
       </c>
       <c r="C17" t="s">
+        <v>157</v>
+      </c>
+      <c r="H17" t="s">
         <v>158</v>
-      </c>
-      <c r="H17" t="s">
-        <v>159</v>
       </c>
       <c r="I17" t="s">
         <v>102</v>
       </c>
       <c r="J17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L17" t="s">
         <v>95</v>
@@ -2472,13 +2469,13 @@
     </row>
     <row r="18" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B18" s="1">
         <v>43502</v>
       </c>
       <c r="C18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D18">
         <v>28.154328</v>
@@ -2493,7 +2490,7 @@
         <v>-82.807177999999993</v>
       </c>
       <c r="H18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I18" t="s">
         <v>102</v>
@@ -2505,7 +2502,7 @@
         <v>95</v>
       </c>
       <c r="M18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N18">
         <v>2</v>
@@ -2550,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="AC18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AD18">
         <v>28.152754000000002</v>
@@ -2573,16 +2570,16 @@
     </row>
     <row r="19" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B19" s="1">
         <v>43497</v>
       </c>
       <c r="C19" t="s">
+        <v>164</v>
+      </c>
+      <c r="H19" t="s">
         <v>165</v>
-      </c>
-      <c r="H19" t="s">
-        <v>166</v>
       </c>
       <c r="I19" t="s">
         <v>102</v>
@@ -2612,7 +2609,7 @@
         <v>1</v>
       </c>
       <c r="U19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V19">
         <v>30.311990000000002</v>
@@ -2659,13 +2656,13 @@
     </row>
     <row r="20" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B20" s="1">
         <v>43501</v>
       </c>
       <c r="C20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D20">
         <v>25.518861000000001</v>
@@ -2680,10 +2677,10 @@
         <v>-81.177914000000001</v>
       </c>
       <c r="H20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J20" t="s">
         <v>103</v>
@@ -2695,7 +2692,7 @@
         <v>95</v>
       </c>
       <c r="M20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N20">
         <v>3</v>
@@ -2719,7 +2716,7 @@
         <v>1</v>
       </c>
       <c r="U20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V20">
         <v>25.47561</v>
@@ -2733,19 +2730,19 @@
     </row>
     <row r="21" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B21" s="1">
         <v>43497</v>
       </c>
       <c r="C21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H21" t="s">
         <v>174</v>
       </c>
-      <c r="H21" t="s">
-        <v>175</v>
-      </c>
       <c r="I21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J21" t="s">
         <v>93</v>
@@ -2757,7 +2754,7 @@
         <v>95</v>
       </c>
       <c r="M21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O21">
         <v>26.2577</v>
@@ -2795,16 +2792,16 @@
     </row>
     <row r="22" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B22" s="1">
         <v>43497</v>
       </c>
       <c r="C22" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" t="s">
         <v>178</v>
-      </c>
-      <c r="H22" t="s">
-        <v>179</v>
       </c>
       <c r="I22" t="s">
         <v>102</v>
@@ -2819,7 +2816,7 @@
         <v>95</v>
       </c>
       <c r="M22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N22">
         <v>8</v>
@@ -2831,7 +2828,7 @@
         <v>2</v>
       </c>
       <c r="Q22" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R22">
         <v>28.087299999999999</v>
@@ -2882,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="AK22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AL22">
         <v>28.0548</v>
@@ -2903,18 +2900,18 @@
         <v>3</v>
       </c>
       <c r="AS22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B23" s="1">
         <v>43498</v>
       </c>
       <c r="C23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D23">
         <v>30.408059999999999</v>
@@ -2929,7 +2926,7 @@
         <v>-81.418469999999999</v>
       </c>
       <c r="H23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I23" t="s">
         <v>102</v>
@@ -2944,7 +2941,7 @@
         <v>95</v>
       </c>
       <c r="M23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N23">
         <v>1</v>
@@ -3003,16 +3000,16 @@
     </row>
     <row r="24" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B24" s="1">
         <v>43502</v>
       </c>
       <c r="C24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I24" t="s">
         <v>102</v>
@@ -3069,7 +3066,7 @@
         <v>6</v>
       </c>
       <c r="AO24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AP24">
         <v>29.875889999999998</v>
@@ -3080,19 +3077,19 @@
     </row>
     <row r="25" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B25" s="1">
         <v>43503</v>
       </c>
       <c r="C25" t="s">
+        <v>190</v>
+      </c>
+      <c r="H25" t="s">
         <v>191</v>
       </c>
-      <c r="H25" t="s">
-        <v>192</v>
-      </c>
       <c r="I25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J25" t="s">
         <v>103</v>
@@ -3133,13 +3130,13 @@
     </row>
     <row r="26" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B26" s="1">
         <v>43497</v>
       </c>
       <c r="C26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D26">
         <v>30.4259959</v>
@@ -3226,7 +3223,7 @@
         <v>2</v>
       </c>
       <c r="AG26" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AH26">
         <v>30.4612719</v>
@@ -3274,7 +3271,7 @@
         <v>4</v>
       </c>
       <c r="AW26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AX26">
         <v>30.487857900000002</v>
@@ -3327,16 +3324,16 @@
     </row>
     <row r="27" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B27" s="1">
         <v>43502</v>
       </c>
       <c r="C27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I27" t="s">
         <v>102</v>
@@ -3380,16 +3377,16 @@
     </row>
     <row r="28" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B28" s="1">
         <v>43497</v>
       </c>
       <c r="C28" t="s">
+        <v>199</v>
+      </c>
+      <c r="H28" t="s">
         <v>200</v>
-      </c>
-      <c r="H28" t="s">
-        <v>201</v>
       </c>
       <c r="K28" t="s">
         <v>104</v>
@@ -3416,27 +3413,27 @@
         <v>2</v>
       </c>
       <c r="U28" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B29" s="1">
         <v>43504</v>
       </c>
       <c r="C29" t="s">
+        <v>203</v>
+      </c>
+      <c r="H29" t="s">
         <v>204</v>
       </c>
-      <c r="H29" t="s">
-        <v>205</v>
-      </c>
       <c r="I29" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K29" t="s">
         <v>104</v>
@@ -3454,18 +3451,18 @@
         <v>16</v>
       </c>
       <c r="Q29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B30" s="1">
         <v>43497</v>
       </c>
       <c r="C30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H30" t="s">
         <v>114</v>
@@ -3489,18 +3486,18 @@
         <v>1</v>
       </c>
       <c r="Q30" t="s">
-        <v>209</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B31" s="1">
         <v>43497</v>
       </c>
       <c r="C31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H31" t="s">
         <v>107</v>
@@ -3527,18 +3524,18 @@
         <v>1</v>
       </c>
       <c r="Q31" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32" spans="1:65" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B32" s="1">
         <v>43501</v>
       </c>
       <c r="C32" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H32" t="s">
         <v>125</v>
@@ -3576,9 +3573,7 @@
       <c r="T32">
         <v>28</v>
       </c>
-      <c r="U32" s="2" t="s">
-        <v>213</v>
-      </c>
+      <c r="U32" s="2"/>
       <c r="V32">
         <v>27.646270000000001</v>
       </c>
@@ -3589,7 +3584,7 @@
         <v>3</v>
       </c>
       <c r="Y32" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Z32">
         <v>27.645700000000001</v>
@@ -3630,13 +3625,13 @@
     </row>
     <row r="33" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B33" s="1">
         <v>43503</v>
       </c>
       <c r="C33" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D33">
         <v>29.513390000000001</v>
@@ -3651,13 +3646,13 @@
         <v>-83.369552999999996</v>
       </c>
       <c r="H33" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I33" t="s">
         <v>102</v>
       </c>
       <c r="J33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K33" t="s">
         <v>104</v>
@@ -3666,7 +3661,7 @@
         <v>95</v>
       </c>
       <c r="M33" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N33">
         <v>2</v>
@@ -3680,19 +3675,19 @@
     </row>
     <row r="34" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B34" s="1">
         <v>43501</v>
       </c>
       <c r="C34" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H34" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I34" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J34" t="s">
         <v>103</v>
@@ -3721,22 +3716,22 @@
     </row>
     <row r="35" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B35" s="1">
         <v>43504</v>
       </c>
       <c r="C35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H35" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K35" t="s">
         <v>104</v>
@@ -3754,27 +3749,27 @@
         <v>18</v>
       </c>
       <c r="Q35" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B36" s="1">
         <v>43501</v>
       </c>
       <c r="C36" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H36" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I36" t="s">
         <v>92</v>
       </c>
       <c r="J36" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K36" t="s">
         <v>104</v>
@@ -3804,7 +3799,7 @@
         <v>7</v>
       </c>
       <c r="U36" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="V36">
         <v>29.67652</v>
@@ -3845,22 +3840,22 @@
     </row>
     <row r="37" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B37" s="1">
         <v>43501</v>
       </c>
       <c r="C37" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H37" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J37" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K37" t="s">
         <v>104</v>
@@ -3908,7 +3903,7 @@
         <v>3</v>
       </c>
       <c r="AK37" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AL37">
         <v>29.7593</v>
@@ -3926,7 +3921,7 @@
         <v>3</v>
       </c>
       <c r="AS37" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AT37">
         <v>29.760390000000001</v>
@@ -3943,22 +3938,22 @@
     </row>
     <row r="38" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B38" s="1">
         <v>43501</v>
       </c>
       <c r="C38" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H38" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I38" t="s">
         <v>102</v>
       </c>
       <c r="J38" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K38" t="s">
         <v>104</v>
@@ -3976,21 +3971,21 @@
         <v>3</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
     </row>
     <row r="39" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B39" s="1">
         <v>43497</v>
       </c>
       <c r="C39" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H39" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I39" t="s">
         <v>102</v>
@@ -4005,7 +4000,7 @@
         <v>95</v>
       </c>
       <c r="M39" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="N39">
         <v>47</v>
@@ -4050,7 +4045,7 @@
         <v>17</v>
       </c>
       <c r="AC39" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AD39">
         <v>28.11552</v>
@@ -4085,16 +4080,16 @@
     </row>
     <row r="40" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B40" s="1">
         <v>43499</v>
       </c>
       <c r="C40" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H40" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="I40" t="s">
         <v>102</v>
@@ -4118,7 +4113,7 @@
         <v>1</v>
       </c>
       <c r="Q40" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="R40">
         <v>30.055319999999998</v>
@@ -4139,21 +4134,21 @@
         <v>1</v>
       </c>
       <c r="Y40" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="41" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B41" s="1">
         <v>43497</v>
       </c>
       <c r="C41" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I41" t="s">
         <v>102</v>
@@ -4168,7 +4163,7 @@
         <v>95</v>
       </c>
       <c r="M41" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N41">
         <v>3</v>
@@ -4281,16 +4276,16 @@
     </row>
     <row r="42" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B42" s="1">
         <v>43499</v>
       </c>
       <c r="C42" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H42" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K42" t="s">
         <v>104</v>
@@ -4308,7 +4303,7 @@
         <v>12</v>
       </c>
       <c r="Q42" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
